--- a/sheets/S08A22P243.xlsx
+++ b/sheets/S08A22P243.xlsx
@@ -28209,7 +28209,7 @@
         <v>13</v>
       </c>
       <c r="G830" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H830" t="s">
         <v>15</v>
@@ -28235,7 +28235,7 @@
         <v>13</v>
       </c>
       <c r="G831" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H831" t="s">
         <v>15</v>
@@ -28261,7 +28261,7 @@
         <v>13</v>
       </c>
       <c r="G832" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H832" t="s">
         <v>15</v>
@@ -28287,7 +28287,7 @@
         <v>13</v>
       </c>
       <c r="G833" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H833" t="s">
         <v>15</v>
@@ -28313,7 +28313,7 @@
         <v>13</v>
       </c>
       <c r="G834" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H834" t="s">
         <v>15</v>
@@ -28339,7 +28339,7 @@
         <v>13</v>
       </c>
       <c r="G835" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H835" t="s">
         <v>15</v>
@@ -28365,7 +28365,7 @@
         <v>13</v>
       </c>
       <c r="G836" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H836" t="s">
         <v>15</v>
@@ -28391,7 +28391,7 @@
         <v>13</v>
       </c>
       <c r="G837" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H837" t="s">
         <v>15</v>
@@ -28417,7 +28417,7 @@
         <v>13</v>
       </c>
       <c r="G838" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H838" t="s">
         <v>15</v>
@@ -28443,7 +28443,7 @@
         <v>13</v>
       </c>
       <c r="G839" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H839" t="s">
         <v>15</v>
@@ -28469,7 +28469,7 @@
         <v>13</v>
       </c>
       <c r="G840" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H840" t="s">
         <v>15</v>
@@ -28495,7 +28495,7 @@
         <v>13</v>
       </c>
       <c r="G841" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H841" t="s">
         <v>15</v>
@@ -28521,7 +28521,7 @@
         <v>13</v>
       </c>
       <c r="G842" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H842" t="s">
         <v>15</v>
@@ -28547,7 +28547,7 @@
         <v>13</v>
       </c>
       <c r="G843" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H843" t="s">
         <v>15</v>
@@ -28573,7 +28573,7 @@
         <v>13</v>
       </c>
       <c r="G844" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H844" t="s">
         <v>15</v>
@@ -28599,7 +28599,7 @@
         <v>13</v>
       </c>
       <c r="G845" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H845" t="s">
         <v>15</v>
@@ -28625,7 +28625,7 @@
         <v>13</v>
       </c>
       <c r="G846" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H846" t="s">
         <v>15</v>
@@ -28651,7 +28651,7 @@
         <v>13</v>
       </c>
       <c r="G847" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H847" t="s">
         <v>15</v>
@@ -28677,7 +28677,7 @@
         <v>13</v>
       </c>
       <c r="G848" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H848" t="s">
         <v>15</v>
@@ -28703,7 +28703,7 @@
         <v>13</v>
       </c>
       <c r="G849" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H849" t="s">
         <v>15</v>
@@ -28729,7 +28729,7 @@
         <v>13</v>
       </c>
       <c r="G850" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H850" t="s">
         <v>15</v>
@@ -28755,7 +28755,7 @@
         <v>13</v>
       </c>
       <c r="G851" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H851" t="s">
         <v>15</v>
@@ -28781,7 +28781,7 @@
         <v>13</v>
       </c>
       <c r="G852" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H852" t="s">
         <v>15</v>
@@ -28807,7 +28807,7 @@
         <v>13</v>
       </c>
       <c r="G853" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H853" t="s">
         <v>15</v>
@@ -28833,7 +28833,7 @@
         <v>13</v>
       </c>
       <c r="G854" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H854" t="s">
         <v>15</v>
@@ -28859,7 +28859,7 @@
         <v>13</v>
       </c>
       <c r="G855" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H855" t="s">
         <v>15</v>
@@ -28885,7 +28885,7 @@
         <v>13</v>
       </c>
       <c r="G856" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H856" t="s">
         <v>15</v>
@@ -28911,7 +28911,7 @@
         <v>13</v>
       </c>
       <c r="G857" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H857" t="s">
         <v>15</v>
@@ -28937,7 +28937,7 @@
         <v>13</v>
       </c>
       <c r="G858" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H858" t="s">
         <v>15</v>
@@ -30523,7 +30523,7 @@
         <v>13</v>
       </c>
       <c r="G919" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H919" t="s">
         <v>15</v>
@@ -30549,7 +30549,7 @@
         <v>13</v>
       </c>
       <c r="G920" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H920" t="s">
         <v>15</v>
@@ -30575,7 +30575,7 @@
         <v>13</v>
       </c>
       <c r="G921" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H921" t="s">
         <v>15</v>
@@ -30601,7 +30601,7 @@
         <v>13</v>
       </c>
       <c r="G922" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H922" t="s">
         <v>15</v>
@@ -30627,7 +30627,7 @@
         <v>13</v>
       </c>
       <c r="G923" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H923" t="s">
         <v>15</v>
@@ -30653,7 +30653,7 @@
         <v>13</v>
       </c>
       <c r="G924" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H924" t="s">
         <v>15</v>
@@ -30679,7 +30679,7 @@
         <v>13</v>
       </c>
       <c r="G925" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H925" t="s">
         <v>15</v>
@@ -30705,7 +30705,7 @@
         <v>13</v>
       </c>
       <c r="G926" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H926" t="s">
         <v>15</v>
